--- a/data/trans_orig/IP22C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22C-Estudios-trans_orig.xlsx
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8085</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12884</t>
+          <t>12885</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>18341</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23819</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75613</t>
+          <t>75350</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>81838</t>
+          <t>81933</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89499</t>
+          <t>89033</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>96501</t>
+          <t>96374</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>167648</t>
+          <t>167668</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>177386</t>
+          <t>176906</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>13451</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25540</t>
+          <t>25085</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30435</t>
+          <t>30426</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32529</t>
+          <t>33069</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37280</t>
+          <t>37286</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60840</t>
+          <t>60625</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67567</t>
+          <t>67559</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4705</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114183</t>
+          <t>114541</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122533</t>
+          <t>122677</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135007</t>
+          <t>134622</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>145086</t>
+          <t>144948</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>252111</t>
+          <t>252863</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>265067</t>
+          <t>265583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>13893</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21503</t>
+          <t>21213</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>14344</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21108</t>
+          <t>21461</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25592</t>
+          <t>25588</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38153</t>
+          <t>38961</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43976</t>
+          <t>43972</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>569</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85759</t>
+          <t>86291</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94915</t>
+          <t>95171</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>118244</t>
+          <t>118656</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>128737</t>
+          <t>128911</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>208108</t>
+          <t>208410</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>221636</t>
+          <t>221829</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>12410</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17503</t>
+          <t>17091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>12619</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26340</t>
+          <t>26038</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33499</t>
+          <t>32840</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>35230</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39991</t>
+          <t>40003</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70473</t>
+          <t>70829</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77070</t>
+          <t>77000</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>619</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139332</t>
+          <t>139443</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149934</t>
+          <t>149415</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>180640</t>
+          <t>180717</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>192555</t>
+          <t>192807</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>324109</t>
+          <t>323174</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>340040</t>
+          <t>340153</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>15460</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9971</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21886</t>
+          <t>21809</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33320</t>
+          <t>34255</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>12816</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17139</t>
+          <t>17142</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>565</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>546</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6848</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63694</t>
+          <t>64532</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71986</t>
+          <t>72135</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61420</t>
+          <t>61490</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71623</t>
+          <t>71853</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>128852</t>
+          <t>129047</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>142149</t>
+          <t>142150</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>13304</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7296</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18993</t>
+          <t>18073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>556</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>562</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>23444</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29519</t>
+          <t>29470</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18793</t>
+          <t>18658</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24317</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45104</t>
+          <t>44944</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52740</t>
+          <t>52714</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>8652</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99191</t>
+          <t>99877</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109309</t>
+          <t>109689</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90401</t>
+          <t>90483</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101999</t>
+          <t>102156</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>193632</t>
+          <t>193585</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>209572</t>
+          <t>208802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>24999</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14970</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>509</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51403</t>
+          <t>51268</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58119</t>
+          <t>58076</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60073</t>
+          <t>60341</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68867</t>
+          <t>68970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>114389</t>
+          <t>114589</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>125556</t>
+          <t>125467</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25880</t>
+          <t>25771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21752</t>
+          <t>21749</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28868</t>
+          <t>28771</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45311</t>
+          <t>45603</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53579</t>
+          <t>53800</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>163</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8375</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>9883</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>735</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83094</t>
+          <t>82879</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92466</t>
+          <t>92389</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95364</t>
+          <t>94476</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106112</t>
+          <t>106010</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>182002</t>
+          <t>181580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>196902</t>
+          <t>196510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>22112</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP22C-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -841,69 +841,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>10877</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8033</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12882</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>80,22%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>59,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>10864</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8997</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9053</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>11440</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,96%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>78,65%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>79,13%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10877</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>8085</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>12885</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>80,22%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>59,63%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>95,03%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>32</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18341</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>23739</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -949,72 +949,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2682</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5526</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>19,78%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,99%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>40,75%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>576</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2443</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2387</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,04%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>21,35%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2682</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5474</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>19,78%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>4,97%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13559</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13559</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13559</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11440</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>11440</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>11440</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>13559</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>13559</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>13559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1179,107 +1179,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4884</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1358</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4859</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4096</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4143</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>93763</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89000</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96843</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>94,82%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>90,01%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>97,94%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>79302</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>75350</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>81933</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>74853</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>81863</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>94,76%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>90,04%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>93763</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>89033</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96374</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>94,82%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>167668</t>
+          <t>167379</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>176906</t>
+          <t>177004</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -1405,72 +1405,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3761</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8073</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4385</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1754</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8337</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1824</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8834</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,24%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3761</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7501</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>13145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>98882</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>98882</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>98882</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>83687</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>83687</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>83687</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>98882</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>98882</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>98882</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1635,107 +1635,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>778</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3871</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4245</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>2,51%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,46%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>13,66%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>3893</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>778</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>3154</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -1748,74 +1748,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>35906</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>32516</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>37285</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>94,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>85,69%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>28983</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>25085</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>30426</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>25886</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>30427</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>93,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>80,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>83,32%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>97,94%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>35906</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>33069</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>37286</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>94,62%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>87,14%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>98,26%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>98</t>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60625</t>
+          <t>59886</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67559</t>
+          <t>67605</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -1861,72 +1861,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2042</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5432</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>14,31%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1306</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4359</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4037</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>4,2%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2042</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4879</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>37948</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>37948</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>37948</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>31068</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>31068</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>31068</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>37948</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>37948</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>37948</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2091,72 +2091,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4786</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>778</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4655</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3663</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4735</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -2204,72 +2204,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>140545</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>135232</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>144965</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>119149</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>114541</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>122677</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>114370</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>122457</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,42%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,76%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>140545</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>134622</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>144948</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>252863</t>
+          <t>252379</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>265583</t>
+          <t>265372</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -2317,72 +2317,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8486</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4663</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13694</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>6268</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2915</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10609</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3163</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>10830</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>4,97%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>8486</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>4469</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>13893</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21213</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>150389</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>150389</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>150389</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>126195</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>126195</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>126195</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>150389</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>150389</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>150389</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2610,7 +2610,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2891,74 +2891,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24343</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21611</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25582</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,06%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>82,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,8%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>17718</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14344</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15461</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>18428</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,15%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>77,84%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>83,9%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24343</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>21461</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25588</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>82,05%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>60</t>
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38961</t>
+          <t>38726</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43972</t>
+          <t>43973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3004,72 +3004,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1814</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4546</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>17,38%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4084</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2967</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,85%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>22,16%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1814</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>569</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4696</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -3117,57 +3117,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26157</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26157</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26157</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>18428</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>18428</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>18428</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26157</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>26157</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>26157</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>124444</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>117998</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>128598</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>86,92%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>94,73%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>91559</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>86291</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>95171</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>86149</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>95089</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>92,76%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>87,43%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>124444</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>118656</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>128911</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>208410</t>
+          <t>208480</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>221829</t>
+          <t>221960</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11303</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7149</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17749</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,27%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,08%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7142</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3530</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12410</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3612</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12552</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,24%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11303</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6836</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17091</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12619</t>
+          <t>12488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26038</t>
+          <t>25968</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>135747</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>135747</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>135747</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>98701</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>98701</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>98701</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>135747</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>135747</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>135747</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3803,74 +3803,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>38533</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34981</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>39996</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>94,86%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>86,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>98,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>36387</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>32840</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>33491</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>37774</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>96,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>86,94%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>88,66%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>38533</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>35230</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>40003</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>94,86%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>86,73%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>105</t>
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70829</t>
+          <t>70849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77000</t>
+          <t>77079</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2089</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5641</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1387</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4934</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4283</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>3,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2089</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5392</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>40622</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>40622</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>40622</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>37774</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>37774</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>37774</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>40622</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>40622</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>40622</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>187320</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>180590</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>192767</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,49%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>145664</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>139443</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>149415</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>139157</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>149578</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,04%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,02%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,46%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>187320</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>180717</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>192807</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,49%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>323174</t>
+          <t>324787</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>340153</t>
+          <t>339929</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15206</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9759</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>21936</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7,51%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10,83%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>9239</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>5488</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>15460</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>5325</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>15746</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>5,96%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>15206</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>9719</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>21809</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>7,51%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>17500</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34255</t>
+          <t>32642</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>202526</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>202526</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>202526</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>154903</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>154903</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>154903</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>202526</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>202526</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>202526</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4665,7 +4665,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4946,74 +4946,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6731</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7423</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>8967</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6619</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6569</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>10284</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>87,19%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>64,36%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>63,88%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6731</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4370</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7423</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>90,68%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>58,87%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>23</t>
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12816</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17142</t>
+          <t>17158</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -5059,72 +5059,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2923</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>39,38%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1317</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3715</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>12,81%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>35,64%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3053</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>549</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -5172,57 +5172,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7423</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7423</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7423</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>10284</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>10284</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>10284</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7423</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7423</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7423</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5289,72 +5289,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6273</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2457</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6249</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6475</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>3,28%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>6340</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -5402,72 +5402,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67591</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>61868</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>72026</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>86,37%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>79,05%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>69032</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>64532</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>72135</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>63961</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>71914</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>92,11%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>86,11%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>96,25%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>67591</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>61490</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>71853</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>86,37%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>129047</t>
+          <t>129230</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>142150</t>
+          <t>142278</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>
@@ -5515,72 +5515,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8248</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4665</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13830</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,67%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3453</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1253</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7514</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7423</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,61%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8248</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4499</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13304</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,54%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>18236</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -5628,57 +5628,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>78260</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>78260</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>78260</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>74942</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>74942</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>74942</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>78260</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>78260</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>78260</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5745,74 +5745,74 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>1793</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>556</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4874</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4873</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>5,83%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>15,85%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>567</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -5858,72 +5858,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>22573</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18917</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>24301</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>90,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>75,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>97,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>27188</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>23444</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29470</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>23568</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>29507</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>88,44%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>76,26%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>95,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>22573</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>18658</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>24303</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>90,19%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44944</t>
+          <t>45532</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52714</t>
+          <t>53049</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -5976,67 +5976,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>2456</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>24,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>1761</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>533</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4788</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4445</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>5,73%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,57%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2456</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6371</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>9,81%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -6084,57 +6084,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>25029</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>25029</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>25029</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>30742</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>30742</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>30742</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>25029</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>25029</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>25029</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6201,72 +6201,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7461</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,74%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>4250</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1741</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8205</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8341</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,66%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7361</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -6314,72 +6314,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>96894</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>89766</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>101783</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,52%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,08%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>91,94%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>105187</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>99877</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>109689</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>99708</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>109629</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>90,7%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>86,12%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>96894</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>90483</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>102156</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>87,52%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>193585</t>
+          <t>193205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>208802</t>
+          <t>208934</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -6427,72 +6427,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11395</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7020</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>17946</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10,29%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16,21%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>6531</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3265</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>11257</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>11392</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>5,63%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>11395</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>6774</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>17562</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>12242</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24999</t>
+          <t>26359</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -6540,57 +6540,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>110711</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>110711</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>110711</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>115968</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>115968</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>115968</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>110711</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>110711</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>110711</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6720,7 +6720,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7001,74 +7001,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8358</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5174</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9296</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,91%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>55,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9096</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5371</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9911</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>91,77%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>54,19%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4271</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4961</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>86,1%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>42,63%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>9734</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6637</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10639</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,5%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>62,38%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>18</t>
@@ -7076,27 +7076,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>18830</t>
+          <t>12630</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>938</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>690</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -7199,12 +7199,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -7227,57 +7227,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9296</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9296</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9296</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9911</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9911</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9911</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7344,72 +7344,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3462</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5,34%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2549</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1796</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>6421</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>413</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -7457,72 +7457,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>60729</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>56396</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>63358</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>93,72%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>87,03%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>55576</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>51268</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>58076</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>92,66%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>85,47%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>96,82%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65644</t>
+          <t>52748</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60341</t>
+          <t>48280</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68970</t>
+          <t>55205</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>121220</t>
+          <t>113478</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>114589</t>
+          <t>107799</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>125467</t>
+          <t>117443</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6984</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3914</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1507</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8219</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,53%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -7683,57 +7683,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>64797</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>64797</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>64797</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>59981</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>59981</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>59981</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70756</t>
+          <t>57009</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70756</t>
+          <t>57009</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70756</t>
+          <t>57009</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>130737</t>
+          <t>121807</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130737</t>
+          <t>121807</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130737</t>
+          <t>121807</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7800,107 +7800,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3790</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4123</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>15,36%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>3867</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>3477</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -7913,72 +7913,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23576</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19544</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25626</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>87,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>72,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>95,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>24181</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20779</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>25771</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>78,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>97,23%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>24304</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>26170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>50490</t>
+          <t>47880</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45603</t>
+          <t>43075</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53800</t>
+          <t>50947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -8026,72 +8026,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3364</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7396</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>27,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4689</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,69%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>349</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9883</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -8139,57 +8139,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>26940</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>26940</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>26940</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>26505</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>26505</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>26505</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30127</t>
+          <t>26843</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30127</t>
+          <t>26843</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30127</t>
+          <t>26843</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>56632</t>
+          <t>53783</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>56632</t>
+          <t>53783</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>56632</t>
+          <t>53783</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>868</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>88853</t>
+          <t>92664</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82879</t>
+          <t>86230</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92389</t>
+          <t>96386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>101687</t>
+          <t>81324</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94476</t>
+          <t>75708</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106010</t>
+          <t>84839</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>190540</t>
+          <t>173987</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181580</t>
+          <t>166324</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>196510</t>
+          <t>180012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>14192</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8997</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>20423</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>96398</t>
+          <t>101034</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96398</t>
+          <t>101034</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96398</t>
+          <t>101034</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>111522</t>
+          <t>88813</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>111522</t>
+          <t>88813</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111522</t>
+          <t>88813</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>207919</t>
+          <t>189847</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>207919</t>
+          <t>189847</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>207919</t>
+          <t>189847</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
